--- a/07-control-framework/Duckworks_AI_Control_Library_v1.0.xlsx
+++ b/07-control-framework/Duckworks_AI_Control_Library_v1.0.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R69f14c19613b4ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Library" sheetId="2" r:id="Rf78b99c902a444dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Coverage" sheetId="3" r:id="R94a3ed425ba94f32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Sources" sheetId="4" r:id="R0fdaf13657c548ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="5" r:id="R0e4812ec9a714f4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" r:id="R5c77080417da4353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3e8f9a600138494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Library" sheetId="2" r:id="R65fe96ca48604139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Coverage" sheetId="3" r:id="Rbbe3272761614435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Sources" sheetId="4" r:id="Rb3a1b1bab1f74bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="5" r:id="Rfbc4abe05f424d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" r:id="Rc19d113121f547ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R988c822c32e846de"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50ece23cc75c4e18"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2605,10 +2605,10 @@
         <x:v>NIST AI RMF: MEASURE / MANAGE; NIST AI 600-1 GenAI Profile; ISO/IEC 27001: access control, data leakage prevention, logging and secure development; ENISA AI cybersecurity guidance; OWASP GenAI Security guidance</x:v>
       </x:c>
       <x:c r="O36" s="26" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Partially Implemented</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Planned - target treatment</x:v>
+        <x:v>Partially implemented - executable synthetic permission-regression control, seeded-defect detection, exception/gate handling and remediation retest are demonstrated; production identity/connector/DLP/SIEM integration, scheduled operating history and production operating effectiveness remain unvalidated</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3150,7 +3150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44f47766d1684539"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R893c32b0229a4cea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3959,7 +3959,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75850c4d7fe9474b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b9555d9bda24b55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4286,7 +4286,7 @@
         <x:v>Partially Implemented</x:v>
       </x:c>
       <x:c r="E5" s="16" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4301,8 +4301,7 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="E6" s="16" t="n">
-        <x:f>COUNTIF('Control Library'!$O$2:$O$46,"Planned")</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4529,6 +4528,6 @@
     <x:mergeCell ref="A1:N1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e3ea1461794430f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54d415bae83c40b2"/>
 </x:worksheet>
 </file>
--- a/07-control-framework/Duckworks_AI_Control_Library_v1.0.xlsx
+++ b/07-control-framework/Duckworks_AI_Control_Library_v1.0.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3e8f9a600138494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Library" sheetId="2" r:id="R65fe96ca48604139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Coverage" sheetId="3" r:id="Rbbe3272761614435"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Sources" sheetId="4" r:id="Rb3a1b1bab1f74bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="5" r:id="Rfbc4abe05f424d30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" r:id="Rc19d113121f547ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R4562dad5d9b9446b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Library" sheetId="2" r:id="R5b7b3683c7c145bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Coverage" sheetId="3" r:id="R2195d8bc013a411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Sources" sheetId="4" r:id="R6a4200db46414539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Legend" sheetId="5" r:id="R42eee74619b54c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" r:id="Ra55a2399a8a846b1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50ece23cc75c4e18"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf335969b7f4b4440"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2255,10 +2255,10 @@
         <x:v>NIST AI RMF: MAP / MEASURE / MANAGE; ISO/IEC 42005: AI impact assessment; ISO/IEC 42001: impact/risk governance; ISO/IEC 23894: AI risk treatment</x:v>
       </x:c>
       <x:c r="O29" s="26" t="str">
-        <x:v>Not Implemented</x:v>
+        <x:v>Partially Implemented</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Not implemented - deployment remains blocked</x:v>
+        <x:v>Partially implemented - executable synthetic fairness/adverse-impact test demonstrates feature allow-list checking, matched-pair diagnostics, seeded unapproved-feature detection, deployment blocking, remediation and retest; production feature governance, lawful fairness-data methodology, real applicant outcomes, legal compliance and sustained operating effectiveness remain unvalidated</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -3150,7 +3150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R893c32b0229a4cea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re86f0c83aa5e422e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3959,7 +3959,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b9555d9bda24b55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3feb4a8348504677"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4286,7 +4286,7 @@
         <x:v>Partially Implemented</x:v>
       </x:c>
       <x:c r="E5" s="16" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4316,8 +4316,7 @@
         <x:v>Not Implemented</x:v>
       </x:c>
       <x:c r="E7" s="16" t="n">
-        <x:f>COUNTIF('Control Library'!$O$2:$O$46,"Not Implemented")</x:f>
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4528,6 +4527,6 @@
     <x:mergeCell ref="A1:N1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54d415bae83c40b2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe045d38c7cf4789"/>
 </x:worksheet>
 </file>